--- a/exports/BEL_full_report.xlsx
+++ b/exports/BEL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>3.5</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>69.90000000000001</v>
+        <v>68.95</v>
       </c>
       <c r="I2" t="n">
         <v>69.33867580924955</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>0.79</v>
+        <v>-0.58</v>
       </c>
       <c r="L2" t="n">
-        <v>0.36</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>0.43</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.96</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44617.55208333334</v>
+        <v>44620.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>66.65000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="I3" t="n">
         <v>67.39594816039926</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K3" t="n">
-        <v>3.34</v>
+        <v>-0.36</v>
       </c>
       <c r="L3" t="n">
         <v>5.22</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.64</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44680.38541666666</v>
+        <v>44680.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>80.40000000000001</v>
+        <v>79.25</v>
       </c>
       <c r="I4" t="n">
         <v>79.34574802348637</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>60</v>
+        <v>60.16666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>16.18</v>
+        <v>14.52</v>
       </c>
       <c r="L4" t="n">
         <v>5.49</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.74</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44701.38541666666</v>
+        <v>44701.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>78.05</v>
+        <v>78.7</v>
       </c>
       <c r="I5" t="n">
         <v>78.14905357741601</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K5" t="n">
-        <v>1.51</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>1.58</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.94</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44728.38541666666</v>
+        <v>44728.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>78</v>
+        <v>77.55</v>
       </c>
       <c r="I6" t="n">
         <v>77.58807955363392</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>26.83333333333333</v>
+        <v>27</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.89</v>
+        <v>-1.46</v>
       </c>
       <c r="L6" t="n">
         <v>6.8</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>6.97</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44757.38541666666</v>
+        <v>44757.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>80.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>80.32006045123224</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.42</v>
+        <v>-5.87</v>
       </c>
       <c r="L7" t="n">
-        <v>4.58</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
         <v>0.93</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.58</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>110.15</v>
+        <v>107.45</v>
       </c>
       <c r="I8" t="n">
         <v>107.6635256198412</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>69</v>
+        <v>69.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>34.17</v>
+        <v>30.88</v>
       </c>
       <c r="L8" t="n">
         <v>2.62</v>
@@ -897,7 +992,7 @@
         <v>0.98</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>3.13</v>
       </c>
       <c r="O8" t="n">
         <v>3.73</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.98</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44841.38541666666</v>
+        <v>44841.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>105.05</v>
+        <v>106.25</v>
       </c>
       <c r="I9" t="n">
         <v>106.0732321580177</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>2.23</v>
+        <v>1.12</v>
       </c>
       <c r="L9" t="n">
         <v>3.3</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.49</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44894.55208333334</v>
+        <v>44895.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>105.5</v>
+        <v>104.6</v>
       </c>
       <c r="I10" t="n">
         <v>104.8730385358382</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>53</v>
+        <v>53.83333333333334</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.71</v>
+        <v>-1.55</v>
       </c>
       <c r="L10" t="n">
         <v>5.93</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>5.47</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44943.38541666666</v>
+        <v>44943.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>102.2</v>
+        <v>102.9</v>
       </c>
       <c r="I11" t="n">
         <v>102.4707773330599</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K11" t="n">
-        <v>2.29</v>
+        <v>1.63</v>
       </c>
       <c r="L11" t="n">
         <v>3.54</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>4.51</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>99.5</v>
+        <v>93.75</v>
       </c>
       <c r="I12" t="n">
         <v>98.76073587281753</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>8</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.3</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>3.98</v>
+        <v>10.11</v>
       </c>
       <c r="M12" t="n">
         <v>0.78</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>4.52</v>
       </c>
       <c r="O12" t="n">
         <v>0.83</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.35</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44965.38541666666</v>
+        <v>44965.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>95.25</v>
+        <v>96.05</v>
       </c>
       <c r="I13" t="n">
         <v>95.60305971545827</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.6</v>
+        <v>-2.45</v>
       </c>
       <c r="L13" t="n">
         <v>6.29</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>6.82</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44998.38541666666</v>
+        <v>44998.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>93.59999999999999</v>
+        <v>91.95</v>
       </c>
       <c r="I14" t="n">
         <v>93.1850040653373</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>32.83333333333334</v>
+        <v>33</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.55</v>
+        <v>-4.27</v>
       </c>
       <c r="L14" t="n">
-        <v>3.07</v>
+        <v>4.27</v>
       </c>
       <c r="M14" t="n">
         <v>1.31</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>5.1</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45014.55208333334</v>
+        <v>45016.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>91.55</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>94.74305479363471</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>16</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>0.44</v>
+        <v>-5.6</v>
       </c>
       <c r="L15" t="n">
-        <v>2.99</v>
+        <v>6.96</v>
       </c>
       <c r="M15" t="n">
-        <v>2.06</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="O15" t="n">
         <v>-3.21</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.88</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45100.38541666666</v>
+        <v>45100.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>121.4</v>
+        <v>119.9</v>
       </c>
       <c r="I16" t="n">
         <v>120.0397961770678</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>84</v>
+        <v>84.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>25.03</v>
+        <v>23.48</v>
       </c>
       <c r="L16" t="n">
         <v>2.94</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>6.01</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45117.55208333334</v>
+        <v>45118.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>123.1</v>
+        <v>128.35</v>
       </c>
       <c r="I17" t="n">
         <v>125.334369604945</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.67</v>
+        <v>-7.05</v>
       </c>
       <c r="L17" t="n">
-        <v>5.67</v>
+        <v>7.3</v>
       </c>
       <c r="M17" t="n">
         <v>0.92</v>
       </c>
       <c r="N17" t="n">
-        <v>3.04</v>
+        <v>3.57</v>
       </c>
       <c r="O17" t="n">
         <v>-3.31</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.37</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45140.38541666666</v>
+        <v>45140.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>126.25</v>
+        <v>125.5</v>
       </c>
       <c r="I18" t="n">
         <v>126.0549729201602</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.64</v>
+        <v>-2.22</v>
       </c>
       <c r="L18" t="n">
         <v>3.86</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>4.7</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45146.55208333334</v>
+        <v>45147.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>129.25</v>
+        <v>131.15</v>
       </c>
       <c r="I19" t="n">
         <v>130.4750105403746</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.99</v>
+        <v>-4.5</v>
       </c>
       <c r="L19" t="n">
-        <v>3.59</v>
+        <v>4.9</v>
       </c>
       <c r="M19" t="n">
         <v>1.12</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.27</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45180.55208333334</v>
+        <v>45181.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>144.7</v>
+        <v>135.2</v>
       </c>
       <c r="I20" t="n">
         <v>138.0530348485664</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K20" t="n">
-        <v>10.33</v>
+        <v>3.09</v>
       </c>
       <c r="L20" t="n">
         <v>3.35</v>
@@ -1581,7 +1820,7 @@
         <v>0.35</v>
       </c>
       <c r="N20" t="n">
-        <v>2.13</v>
+        <v>6.7</v>
       </c>
       <c r="O20" t="n">
         <v>1.9</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>10.1</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45232.55208333334</v>
+        <v>45233.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>135</v>
+        <v>136.25</v>
       </c>
       <c r="I21" t="n">
         <v>136.0723335851875</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K21" t="n">
-        <v>0.15</v>
+        <v>-0.78</v>
       </c>
       <c r="L21" t="n">
         <v>7.25</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.86</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45322.55208333334</v>
+        <v>45323.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>186.25</v>
+        <v>183.15</v>
       </c>
       <c r="I22" t="n">
         <v>184.006915513219</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>89.16666666666667</v>
+        <v>90</v>
       </c>
       <c r="K22" t="n">
-        <v>36.7</v>
+        <v>34.42</v>
       </c>
       <c r="L22" t="n">
         <v>1.1</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>7.51</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45337.55208333334</v>
+        <v>45338.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>186</v>
+        <v>189.2</v>
       </c>
       <c r="I23" t="n">
         <v>187.393661666557</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.56</v>
+        <v>-3.3</v>
       </c>
       <c r="L23" t="n">
-        <v>2.87</v>
+        <v>3.44</v>
       </c>
       <c r="M23" t="n">
-        <v>1.27</v>
+        <v>1.61</v>
       </c>
       <c r="N23" t="n">
         <v>3.12</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.53</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>204.25</v>
+        <v>195.45</v>
       </c>
       <c r="I24" t="n">
         <v>201.9612096482846</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K24" t="n">
-        <v>7.95</v>
+        <v>3.3</v>
       </c>
       <c r="L24" t="n">
         <v>1.56</v>
@@ -1809,7 +2096,7 @@
         <v>0.57</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>7.05</v>
       </c>
       <c r="O24" t="n">
         <v>1.08</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>10.1</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>201.85</v>
+        <v>207.3</v>
       </c>
       <c r="I25" t="n">
         <v>203.6581110364401</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.27</v>
+        <v>-6.06</v>
       </c>
       <c r="L25" t="n">
-        <v>5.19</v>
+        <v>6.22</v>
       </c>
       <c r="M25" t="n">
-        <v>1.17</v>
+        <v>1.56</v>
       </c>
       <c r="N25" t="n">
-        <v>4.74</v>
+        <v>4.88</v>
       </c>
       <c r="O25" t="n">
         <v>-7.05</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>7.18</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>231.95</v>
+        <v>226.3</v>
       </c>
       <c r="I26" t="n">
         <v>228.0936917190843</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K26" t="n">
-        <v>11.89</v>
+        <v>9.17</v>
       </c>
       <c r="L26" t="n">
         <v>1.71</v>
@@ -1923,7 +2234,7 @@
         <v>1.89</v>
       </c>
       <c r="N26" t="n">
-        <v>1.21</v>
+        <v>1.92</v>
       </c>
       <c r="O26" t="n">
         <v>4.88</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>7.9</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45428.38541666666</v>
+        <v>45428.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>230.1</v>
+        <v>239.6</v>
       </c>
       <c r="I27" t="n">
         <v>238.7281995188238</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.68</v>
+        <v>-5.88</v>
       </c>
       <c r="L27" t="n">
-        <v>5.26</v>
+        <v>6.05</v>
       </c>
       <c r="M27" t="n">
         <v>1.21</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>9.16</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>319.8</v>
+        <v>263</v>
       </c>
       <c r="I28" t="n">
         <v>291.9256803379026</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>33.47</v>
+        <v>9.77</v>
       </c>
       <c r="L28" t="n">
         <v>5.05</v>
       </c>
       <c r="M28" t="n">
-        <v>1.14</v>
+        <v>2.44</v>
       </c>
       <c r="N28" t="n">
-        <v>1.87</v>
+        <v>19.5</v>
       </c>
       <c r="O28" t="n">
         <v>2.72</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>22.02</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45456.55208333334</v>
+        <v>45457.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>302.85</v>
+        <v>307.9</v>
       </c>
       <c r="I29" t="n">
         <v>304.631479033669</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>-15.15</v>
+        <v>-17.07</v>
       </c>
       <c r="L29" t="n">
         <v>18.63</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.77</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45489.55208333334</v>
+        <v>45491.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>326.35</v>
+        <v>315.2</v>
       </c>
       <c r="I30" t="n">
         <v>316.9028939138292</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K30" t="n">
-        <v>5.99</v>
+        <v>2.37</v>
       </c>
       <c r="L30" t="n">
         <v>3.39</v>
@@ -2151,7 +2510,7 @@
         <v>0.24</v>
       </c>
       <c r="N30" t="n">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
         <v>2.29</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>7.61</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45558.55208333334</v>
+        <v>45559.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>286.5</v>
+        <v>290.1</v>
       </c>
       <c r="I31" t="n">
         <v>287.6582417855164</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>67.16666666666667</v>
+        <v>68</v>
       </c>
       <c r="K31" t="n">
-        <v>9.109999999999999</v>
+        <v>7.96</v>
       </c>
       <c r="L31" t="n">
         <v>3.65</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.26</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45568.38541666666</v>
+        <v>45568.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>279.3</v>
+        <v>278.8</v>
       </c>
       <c r="I32" t="n">
         <v>278.954958144902</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.72</v>
+        <v>-3.9</v>
       </c>
       <c r="L32" t="n">
         <v>5.19</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,25 +2696,25 @@
         <v>5.33</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45574.55208333334</v>
+        <v>45575.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>282.6</v>
+        <v>287.55</v>
       </c>
       <c r="I33" t="n">
         <v>284.2877282630172</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.36</v>
+        <v>-3.14</v>
       </c>
       <c r="L33" t="n">
-        <v>2.8</v>
+        <v>3.87</v>
       </c>
       <c r="M33" t="n">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="N33" t="n">
         <v>5.09</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>6.83</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>281.6</v>
+        <v>274.6</v>
       </c>
       <c r="I34" t="n">
         <v>275.3538518380624</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.07</v>
+        <v>-4.5</v>
       </c>
       <c r="L34" t="n">
-        <v>3.39</v>
+        <v>4.82</v>
       </c>
       <c r="M34" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>1.88</v>
+        <v>3.55</v>
       </c>
       <c r="O34" t="n">
         <v>1.52</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>6.49</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45594.38541666666</v>
+        <v>45594.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>277.3</v>
+        <v>283.3</v>
       </c>
       <c r="I35" t="n">
         <v>281.6286980648252</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.98</v>
+        <v>-3.17</v>
       </c>
       <c r="L35" t="n">
-        <v>2.75</v>
+        <v>3.61</v>
       </c>
       <c r="M35" t="n">
         <v>0.46</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.57</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45614.38541666666</v>
+        <v>45614.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>281</v>
+        <v>278.2</v>
       </c>
       <c r="I36" t="n">
         <v>280.7981238034654</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.8</v>
       </c>
       <c r="L36" t="n">
         <v>2.75</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>7.21</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>281</v>
+        <v>294.7</v>
       </c>
       <c r="I37" t="n">
         <v>293.9175552350331</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.01</v>
+        <v>-5.93</v>
       </c>
       <c r="L37" t="n">
-        <v>2.52</v>
+        <v>7.48</v>
       </c>
       <c r="M37" t="n">
-        <v>0.65</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>2.03</v>
+        <v>4.27</v>
       </c>
       <c r="O37" t="n">
         <v>-1.08</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.85</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>310.2</v>
+        <v>303.5</v>
       </c>
       <c r="I38" t="n">
         <v>305.5817084434524</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K38" t="n">
-        <v>5.26</v>
+        <v>2.99</v>
       </c>
       <c r="L38" t="n">
         <v>2.29</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>4.99</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45673.38541666666</v>
+        <v>45673.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>276.4</v>
+        <v>277.5</v>
       </c>
       <c r="I39" t="n">
         <v>277.3726713101975</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>8.93</v>
+        <v>8.57</v>
       </c>
       <c r="L39" t="n">
         <v>2.34</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>6.23</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45678.55208333334</v>
+        <v>45679.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>279.25</v>
+        <v>268.3</v>
       </c>
       <c r="I40" t="n">
         <v>270.0027268885378</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>0.63</v>
+        <v>-3.32</v>
       </c>
       <c r="L40" t="n">
-        <v>1.24</v>
+        <v>4.04</v>
       </c>
       <c r="M40" t="n">
         <v>0.74</v>
       </c>
       <c r="N40" t="n">
-        <v>2.14</v>
+        <v>3.1</v>
       </c>
       <c r="O40" t="n">
         <v>3.54</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>8.49</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45687.38541666666</v>
+        <v>45687.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>272.2</v>
+        <v>280.1</v>
       </c>
       <c r="I41" t="n">
         <v>278.953658962557</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.45</v>
+        <v>-4.4</v>
       </c>
       <c r="L41" t="n">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="M41" t="n">
         <v>0.32</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.41</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>273.9</v>
+        <v>264.25</v>
       </c>
       <c r="I42" t="n">
         <v>270.0753073345518</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.21</v>
+        <v>-5.66</v>
       </c>
       <c r="L42" t="n">
         <v>6</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>10.48</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45719.55208333334</v>
+        <v>45720.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>257.5</v>
+        <v>264</v>
       </c>
       <c r="I43" t="n">
         <v>262.1944964746037</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
-        <v>2.55</v>
+        <v>0.09</v>
       </c>
       <c r="L43" t="n">
         <v>3.69</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>290.9</v>
+        <v>287</v>
       </c>
       <c r="I44" t="n">
         <v>289.3772535486102</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K44" t="n">
-        <v>10.19</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L44" t="n">
         <v>4.36</v>
       </c>
       <c r="M44" t="n">
-        <v>1.4</v>
+        <v>2.72</v>
       </c>
       <c r="N44" t="n">
         <v>3.46</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.73</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>281</v>
+        <v>286.5</v>
       </c>
       <c r="I45" t="n">
         <v>286.2508989680672</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K45" t="n">
-        <v>2.09</v>
+        <v>0.17</v>
       </c>
       <c r="L45" t="n">
         <v>0.44</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.77</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>413.3</v>
+        <v>411.3</v>
       </c>
       <c r="I46" t="n">
         <v>411.9042295220998</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>90.16666666666667</v>
+        <v>91</v>
       </c>
       <c r="K46" t="n">
-        <v>44.26</v>
+        <v>43.56</v>
       </c>
       <c r="L46" t="n">
         <v>1.34</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>3.66</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>373.05</v>
+        <v>386.1</v>
       </c>
       <c r="I47" t="n">
         <v>379.5551205500215</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K47" t="n">
-        <v>9.300000000000001</v>
+        <v>6.13</v>
       </c>
       <c r="L47" t="n">
         <v>0.46</v>
@@ -3120,7 +3683,7 @@
         <v>1.4</v>
       </c>
       <c r="N47" t="n">
-        <v>3.43</v>
+        <v>4.28</v>
       </c>
       <c r="O47" t="n">
         <v>-1.04</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.61</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45959.38541666666</v>
+        <v>45959.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>408.95</v>
+        <v>407.6</v>
       </c>
       <c r="I48" t="n">
         <v>408.2401395293401</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K48" t="n">
-        <v>5.92</v>
+        <v>5.57</v>
       </c>
       <c r="L48" t="n">
         <v>3.38</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>3.68</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45961.38541666666</v>
+        <v>45961.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>420.65</v>
+        <v>426.4</v>
       </c>
       <c r="I49" t="n">
         <v>422.1692308800492</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.833333333333333</v>
+        <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.2</v>
+        <v>-4.61</v>
       </c>
       <c r="L49" t="n">
-        <v>3.42</v>
+        <v>4.82</v>
       </c>
       <c r="M49" t="n">
         <v>0.88</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>4.78</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45982.55208333334</v>
+        <v>45985.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>417.2</v>
+        <v>407.45</v>
       </c>
       <c r="I50" t="n">
         <v>409.9257420916585</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>21</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.16</v>
+        <v>-4.44</v>
       </c>
       <c r="L50" t="n">
         <v>4.95</v>
@@ -3291,7 +3890,7 @@
         <v>1.09</v>
       </c>
       <c r="N50" t="n">
-        <v>1.62</v>
+        <v>3.43</v>
       </c>
       <c r="O50" t="n">
         <v>3.95</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>4.91</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46013.38541666666</v>
+        <v>46013.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>396.35</v>
+        <v>398.9</v>
       </c>
       <c r="I51" t="n">
         <v>396.357377595861</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="L51" t="n">
         <v>2.88</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>3.77</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46093.55208333334</v>
+        <v>46094.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>453.9</v>
+        <v>436.3</v>
       </c>
       <c r="I52" t="n">
         <v>442.2801374734312</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>80</v>
+        <v>80.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>13.79</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L52" t="n">
         <v>2.34</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>8.52</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>426.95</v>
+        <v>431</v>
       </c>
       <c r="I53" t="n">
         <v>429.5056954063427</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K53" t="n">
-        <v>2.14</v>
+        <v>1.21</v>
       </c>
       <c r="L53" t="n">
         <v>3.69</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.59</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>449.7</v>
+        <v>439.5</v>
       </c>
       <c r="I54" t="n">
         <v>440.7113243118448</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K54" t="n">
-        <v>4.34</v>
+        <v>1.97</v>
       </c>
       <c r="L54" t="n">
         <v>1.51</v>
@@ -3519,7 +4166,7 @@
         <v>2.11</v>
       </c>
       <c r="N54" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="O54" t="n">
         <v>1.69</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.17</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46190.38541666666</v>
+        <v>46190.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>413.65</v>
+        <v>422.25</v>
       </c>
       <c r="I55" t="n">
         <v>419.523816536565</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>54</v>
+        <v>54.16666666666666</v>
       </c>
       <c r="K55" t="n">
-        <v>5.88</v>
+        <v>3.92</v>
       </c>
       <c r="L55" t="n">
         <v>2.66</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>5.07</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46197.38541666666</v>
+        <v>46197.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>416.45</v>
+        <v>413.25</v>
       </c>
       <c r="I56" t="n">
         <v>414.8553835625431</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.37</v>
+        <v>-2.13</v>
       </c>
       <c r="L56" t="n">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="M56" t="n">
         <v>0.07000000000000001</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>4.69</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46240.38541666666</v>
+        <v>46240.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>399</v>
+        <v>399.5</v>
       </c>
       <c r="I57" t="n">
         <v>399.1943649740849</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>42.83333333333334</v>
+        <v>43</v>
       </c>
       <c r="K57" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="L57" t="n">
         <v>4.03</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>3.55</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46276.55208333334</v>
+        <v>46280.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>404.35</v>
+        <v>390.8</v>
       </c>
       <c r="I58" t="n">
         <v>401.060395312659</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>36</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K58" t="n">
-        <v>1.21</v>
+        <v>-2.18</v>
       </c>
       <c r="L58" t="n">
-        <v>0.29</v>
+        <v>2.98</v>
       </c>
       <c r="M58" t="n">
         <v>0.73</v>
       </c>
       <c r="N58" t="n">
-        <v>1.32</v>
+        <v>4.79</v>
       </c>
       <c r="O58" t="n">
         <v>2.65</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>5.34</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>380.15</v>
+        <v>381.9</v>
       </c>
       <c r="I59" t="n">
         <v>381.7731417201819</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K59" t="n">
-        <v>2.73</v>
+        <v>2.28</v>
       </c>
       <c r="L59" t="n">
         <v>3.29</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>4.39</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46317.38541666666</v>
+        <v>46317.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>366.4</v>
+        <v>364.95</v>
       </c>
       <c r="I60" t="n">
         <v>366.2580654697508</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.06</v>
+        <v>-4.44</v>
       </c>
       <c r="L60" t="n">
         <v>5.29</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3921,6 +4652,12 @@
       <c r="Q61" t="n">
         <v>7</v>
       </c>
+      <c r="R61" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6023,7 +6760,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="6">
@@ -6033,7 +6770,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -6043,7 +6780,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>90.2</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
@@ -6053,7 +6790,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6063,7 +6800,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36.6</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="10">
@@ -6073,7 +6810,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61.6</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="11">
@@ -6113,7 +6850,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.43</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="15">
@@ -6123,7 +6860,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.09</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="16">
@@ -6133,7 +6870,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.64</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="17">
@@ -6143,7 +6880,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>44.26</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="18">
@@ -6153,7 +6890,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57.6</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="19">
@@ -6163,7 +6900,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="20">
@@ -6173,7 +6910,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.38</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="21">
@@ -6193,7 +6930,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -6203,7 +6940,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -6213,7 +6950,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="25">
@@ -6233,7 +6970,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.21</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="27">
@@ -6243,7 +6980,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.47</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="28">
@@ -6253,7 +6990,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
